--- a/Res_ConvLSTM/DroughtDataset_model_testing_1755175568_individual_h_6.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1755175568_individual_h_6.xlsx
@@ -658,7 +658,7 @@
         <v>0.008444666370446814</v>
       </c>
       <c r="C2" t="n">
-        <v>38078280</v>
+        <v>6346380</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>38078280</v>
+        <v>6346380</v>
       </c>
       <c r="K2" t="n">
-        <v>27569307</v>
+        <v>4248151</v>
       </c>
       <c r="L2" t="n">
-        <v>16118911</v>
+        <v>2225338</v>
       </c>
       <c r="M2" t="n">
-        <v>4030728</v>
+        <v>490152</v>
       </c>
       <c r="N2" t="n">
-        <v>202321</v>
+        <v>14653</v>
       </c>
       <c r="O2" t="n">
-        <v>2389129</v>
+        <v>298353</v>
       </c>
       <c r="P2" t="n">
-        <v>921319</v>
+        <v>108514</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.999976634979248</v>
+        <v>0.9999968409538269</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9050423502922058</v>
+        <v>0.8274222016334534</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8016678094863892</v>
+        <v>0.6625778675079346</v>
       </c>
       <c r="T2" t="n">
-        <v>0.756703794002533</v>
+        <v>0.5753099322319031</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4354041814804077</v>
+        <v>0.1414628028869629</v>
       </c>
       <c r="V2" t="n">
-        <v>0.7959921360015869</v>
+        <v>0.6231786012649536</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8729580044746399</v>
+        <v>0.7616460919380188</v>
       </c>
       <c r="X2" t="n">
-        <v>38078280</v>
+        <v>6346380</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>38078280</v>
+        <v>6346380</v>
       </c>
       <c r="AF2" t="n">
-        <v>29076132</v>
+        <v>4830872</v>
       </c>
       <c r="AG2" t="n">
-        <v>17922026</v>
+        <v>2998822</v>
       </c>
       <c r="AH2" t="n">
-        <v>4807435</v>
+        <v>802107</v>
       </c>
       <c r="AI2" t="n">
-        <v>354710</v>
+        <v>59151</v>
       </c>
       <c r="AJ2" t="n">
-        <v>2755990</v>
+        <v>459696</v>
       </c>
       <c r="AK2" t="n">
-        <v>1080323</v>
+        <v>180138</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.95653235912323</v>
+        <v>0.9562515616416931</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.911312997341156</v>
+        <v>0.9114683270454407</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8580047488212585</v>
+        <v>0.8577601909637451</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.66214919090271</v>
+        <v>0.6615037322044373</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9019646644592285</v>
+        <v>0.9018846154212952</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314349889755249</v>
+        <v>0.9314607977867126</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.002024449655927808</v>
       </c>
       <c r="C3" t="n">
-        <v>563</v>
+        <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>27569307</v>
+        <v>4248151</v>
       </c>
       <c r="E3" t="n">
-        <v>2745595</v>
+        <v>777358</v>
       </c>
       <c r="F3" t="n">
-        <v>41131</v>
+        <v>17414</v>
       </c>
       <c r="G3" t="n">
-        <v>4441</v>
+        <v>1556</v>
       </c>
       <c r="H3" t="n">
-        <v>2408</v>
+        <v>1071</v>
       </c>
       <c r="I3" t="n">
-        <v>105</v>
+        <v>27</v>
       </c>
       <c r="J3" t="n">
-        <v>60416831</v>
+        <v>10069600</v>
       </c>
       <c r="K3" t="n">
-        <v>65239860</v>
+        <v>10484371</v>
       </c>
       <c r="L3" t="n">
-        <v>74813435</v>
+        <v>11987522</v>
       </c>
       <c r="M3" t="n">
-        <v>91593577</v>
+        <v>15118282</v>
       </c>
       <c r="N3" t="n">
-        <v>97697563</v>
+        <v>16237567</v>
       </c>
       <c r="O3" t="n">
-        <v>94826834</v>
+        <v>15725598</v>
       </c>
       <c r="P3" t="n">
-        <v>97201895</v>
+        <v>16188601</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9079737663269043</v>
+        <v>0.8419549465179443</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8184367418289185</v>
+        <v>0.6753250956535339</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7189436554908752</v>
+        <v>0.5237276554107666</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3774054050445557</v>
+        <v>0.163713350892067</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7815664410591125</v>
+        <v>0.5850116014480591</v>
       </c>
       <c r="W3" t="n">
-        <v>0.794223427772522</v>
+        <v>0.5609698295593262</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>29076132</v>
+        <v>4830872</v>
       </c>
       <c r="Z3" t="n">
-        <v>1194510</v>
+        <v>199161</v>
       </c>
       <c r="AA3" t="n">
-        <v>51498</v>
+        <v>8614</v>
       </c>
       <c r="AB3" t="n">
-        <v>40960</v>
+        <v>6858</v>
       </c>
       <c r="AC3" t="n">
-        <v>270</v>
+        <v>45</v>
       </c>
       <c r="AD3" t="n">
-        <v>180</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>60417720</v>
+        <v>10069620</v>
       </c>
       <c r="AF3" t="n">
-        <v>66811145</v>
+        <v>11149408</v>
       </c>
       <c r="AG3" t="n">
-        <v>77057112</v>
+        <v>12829512</v>
       </c>
       <c r="AH3" t="n">
-        <v>92093936</v>
+        <v>15347098</v>
       </c>
       <c r="AI3" t="n">
-        <v>97778931</v>
+        <v>16296228</v>
       </c>
       <c r="AJ3" t="n">
-        <v>95139602</v>
+        <v>15855995</v>
       </c>
       <c r="AK3" t="n">
-        <v>97256450</v>
+        <v>16209305</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9575998783111572</v>
+        <v>0.9574463367462158</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9099897742271423</v>
+        <v>0.9100549221038818</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8574815392494202</v>
+        <v>0.8570517301559448</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6616687178611755</v>
+        <v>0.6608754992485046</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9015793204307556</v>
+        <v>0.901373565196991</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9312928318977356</v>
+        <v>0.9312344789505005</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.0319545241795172</v>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>2732498</v>
+        <v>835035</v>
       </c>
       <c r="E4" t="n">
-        <v>16118911</v>
+        <v>2225338</v>
       </c>
       <c r="F4" t="n">
-        <v>758433</v>
+        <v>202172</v>
       </c>
       <c r="G4" t="n">
-        <v>26847</v>
+        <v>10573</v>
       </c>
       <c r="H4" t="n">
-        <v>54213</v>
+        <v>20522</v>
       </c>
       <c r="I4" t="n">
-        <v>3850</v>
+        <v>1570</v>
       </c>
       <c r="J4" t="n">
-        <v>889</v>
+        <v>20</v>
       </c>
       <c r="K4" t="n">
-        <v>2892590</v>
+        <v>886049</v>
       </c>
       <c r="L4" t="n">
-        <v>3987810</v>
+        <v>1133268</v>
       </c>
       <c r="M4" t="n">
-        <v>1295964</v>
+        <v>361827</v>
       </c>
       <c r="N4" t="n">
-        <v>262353</v>
+        <v>88929</v>
       </c>
       <c r="O4" t="n">
-        <v>612319</v>
+        <v>180407</v>
       </c>
       <c r="P4" t="n">
-        <v>134080</v>
+        <v>33959</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.999988317489624</v>
+        <v>0.9999983906745911</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9065056443214417</v>
+        <v>0.8346253633499146</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8099654912948608</v>
+        <v>0.6688907146453857</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7373406291007996</v>
+        <v>0.548308253288269</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4043355286121368</v>
+        <v>0.1517769396305084</v>
       </c>
       <c r="V4" t="n">
-        <v>0.7887133359909058</v>
+        <v>0.603492259979248</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8317314982414246</v>
+        <v>0.6460840106010437</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1233664</v>
+        <v>206326</v>
       </c>
       <c r="Z4" t="n">
-        <v>17922026</v>
+        <v>2998822</v>
       </c>
       <c r="AA4" t="n">
-        <v>498690</v>
+        <v>83312</v>
       </c>
       <c r="AB4" t="n">
-        <v>33091</v>
+        <v>5534</v>
       </c>
       <c r="AC4" t="n">
-        <v>6876</v>
+        <v>1148</v>
       </c>
       <c r="AD4" t="n">
-        <v>408</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1321305</v>
+        <v>221012</v>
       </c>
       <c r="AG4" t="n">
-        <v>1744133</v>
+        <v>291278</v>
       </c>
       <c r="AH4" t="n">
-        <v>795605</v>
+        <v>133011</v>
       </c>
       <c r="AI4" t="n">
-        <v>180985</v>
+        <v>30268</v>
       </c>
       <c r="AJ4" t="n">
-        <v>299551</v>
+        <v>50010</v>
       </c>
       <c r="AK4" t="n">
-        <v>79525</v>
+        <v>13255</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9570658206939697</v>
+        <v>0.9568485021591187</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.910650908946991</v>
+        <v>0.9107611179351807</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8577430844306946</v>
+        <v>0.8574058413505554</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6619088649749756</v>
+        <v>0.6611894369125366</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9017719030380249</v>
+        <v>0.9016289710998535</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313638806343079</v>
+        <v>0.9313476085662842</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>171</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>102643</v>
+        <v>35000</v>
       </c>
       <c r="E5" t="n">
-        <v>1067877</v>
+        <v>299777</v>
       </c>
       <c r="F5" t="n">
-        <v>4030728</v>
+        <v>490152</v>
       </c>
       <c r="G5" t="n">
-        <v>96108</v>
+        <v>28830</v>
       </c>
       <c r="H5" t="n">
-        <v>288393</v>
+        <v>75043</v>
       </c>
       <c r="I5" t="n">
-        <v>20539</v>
+        <v>7088</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>2794243</v>
+        <v>797429</v>
       </c>
       <c r="L5" t="n">
-        <v>3575844</v>
+        <v>1069872</v>
       </c>
       <c r="M5" t="n">
-        <v>1575731</v>
+        <v>445739</v>
       </c>
       <c r="N5" t="n">
-        <v>333763</v>
+        <v>74851</v>
       </c>
       <c r="O5" t="n">
-        <v>667718</v>
+        <v>211642</v>
       </c>
       <c r="P5" t="n">
-        <v>238706</v>
+        <v>84926</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999909996986389</v>
+        <v>0.9999988079071045</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9422633051872253</v>
+        <v>0.8974489569664001</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9232085347175598</v>
+        <v>0.8657931089401245</v>
       </c>
       <c r="T5" t="n">
-        <v>0.970844566822052</v>
+        <v>0.9508061408996582</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9939478039741516</v>
+        <v>0.990023136138916</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9870041608810425</v>
+        <v>0.9761178493499756</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9962152242660522</v>
+        <v>0.9927579760551453</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>48367</v>
+        <v>8102</v>
       </c>
       <c r="Z5" t="n">
-        <v>512041</v>
+        <v>85827</v>
       </c>
       <c r="AA5" t="n">
-        <v>4807435</v>
+        <v>802107</v>
       </c>
       <c r="AB5" t="n">
-        <v>59802</v>
+        <v>9994</v>
       </c>
       <c r="AC5" t="n">
-        <v>175016</v>
+        <v>29228</v>
       </c>
       <c r="AD5" t="n">
-        <v>3798</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1287418</v>
+        <v>214708</v>
       </c>
       <c r="AG5" t="n">
-        <v>1772729</v>
+        <v>296388</v>
       </c>
       <c r="AH5" t="n">
-        <v>799024</v>
+        <v>133784</v>
       </c>
       <c r="AI5" t="n">
-        <v>181374</v>
+        <v>30353</v>
       </c>
       <c r="AJ5" t="n">
-        <v>300857</v>
+        <v>50299</v>
       </c>
       <c r="AK5" t="n">
-        <v>79702</v>
+        <v>13302</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9735144376754761</v>
+        <v>0.9734575748443604</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9642943739891052</v>
+        <v>0.9642016291618347</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9838101863861084</v>
+        <v>0.9837478399276733</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963210821151733</v>
+        <v>0.9963071942329407</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9939042329788208</v>
+        <v>0.9938895702362061</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983834028244019</v>
+        <v>0.9983822703361511</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>71</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>55789</v>
+        <v>14810</v>
       </c>
       <c r="E6" t="n">
-        <v>97468</v>
+        <v>21126</v>
       </c>
       <c r="F6" t="n">
-        <v>122371</v>
+        <v>27303</v>
       </c>
       <c r="G6" t="n">
-        <v>202321</v>
+        <v>14653</v>
       </c>
       <c r="H6" t="n">
-        <v>54146</v>
+        <v>10642</v>
       </c>
       <c r="I6" t="n">
-        <v>3918</v>
+        <v>967</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>38939</v>
+        <v>6528</v>
       </c>
       <c r="Z6" t="n">
-        <v>32230</v>
+        <v>5399</v>
       </c>
       <c r="AA6" t="n">
-        <v>65403</v>
+        <v>10952</v>
       </c>
       <c r="AB6" t="n">
-        <v>354710</v>
+        <v>59151</v>
       </c>
       <c r="AC6" t="n">
-        <v>41916</v>
+        <v>6993</v>
       </c>
       <c r="AD6" t="n">
-        <v>2886</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1535</v>
+        <v>1167</v>
       </c>
       <c r="E7" t="n">
-        <v>72790</v>
+        <v>32889</v>
       </c>
       <c r="F7" t="n">
-        <v>359437</v>
+        <v>108580</v>
       </c>
       <c r="G7" t="n">
-        <v>128283</v>
+        <v>44698</v>
       </c>
       <c r="H7" t="n">
-        <v>2389129</v>
+        <v>298353</v>
       </c>
       <c r="I7" t="n">
-        <v>105668</v>
+        <v>24307</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>167</v>
+        <v>28</v>
       </c>
       <c r="Z7" t="n">
-        <v>4866</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>178032</v>
+        <v>29802</v>
       </c>
       <c r="AB7" t="n">
-        <v>45539</v>
+        <v>7616</v>
       </c>
       <c r="AC7" t="n">
-        <v>2755990</v>
+        <v>459696</v>
       </c>
       <c r="AD7" t="n">
-        <v>72253</v>
+        <v>12043</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>76</v>
+        <v>12</v>
       </c>
       <c r="D8" t="n">
-        <v>125</v>
+        <v>37</v>
       </c>
       <c r="E8" t="n">
-        <v>4080</v>
+        <v>2118</v>
       </c>
       <c r="F8" t="n">
-        <v>14592</v>
+        <v>6358</v>
       </c>
       <c r="G8" t="n">
-        <v>6674</v>
+        <v>3272</v>
       </c>
       <c r="H8" t="n">
-        <v>213159</v>
+        <v>73129</v>
       </c>
       <c r="I8" t="n">
-        <v>921319</v>
+        <v>108514</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>168</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>486</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>1982</v>
+        <v>331</v>
       </c>
       <c r="AB8" t="n">
-        <v>1593</v>
+        <v>266</v>
       </c>
       <c r="AC8" t="n">
-        <v>75473</v>
+        <v>12596</v>
       </c>
       <c r="AD8" t="n">
-        <v>1080323</v>
+        <v>180138</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
